--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2415,6 +2415,536 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129000852</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78881</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>406965</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6852180</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129001298</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92792</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>407032</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6852243</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129000850</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79714</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>406963</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6852178</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129000854</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>353</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>406800</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6852913</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129000851</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78882</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>406964</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6852179</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129000852</v>
       </c>
       <c r="B18" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>129001298</v>
       </c>
       <c r="B19" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129000850</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>129000854</v>
       </c>
       <c r="B21" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129000851</v>
       </c>
       <c r="B22" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>129001298</v>
       </c>
       <c r="B19" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2314,7 +2314,7 @@
         <v>128533092</v>
       </c>
       <c r="B17" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129000852</v>
       </c>
       <c r="B18" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>129001298</v>
       </c>
       <c r="B19" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129000850</v>
       </c>
       <c r="B20" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>129000854</v>
       </c>
       <c r="B21" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129000851</v>
       </c>
       <c r="B22" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2420,7 +2420,7 @@
         <v>129000852</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>129001298</v>
       </c>
       <c r="B19" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129000850</v>
       </c>
       <c r="B20" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>129000854</v>
       </c>
       <c r="B21" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129000851</v>
       </c>
       <c r="B22" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>129001298</v>
       </c>
       <c r="B19" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2420,7 +2420,7 @@
         <v>129000852</v>
       </c>
       <c r="B18" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>129001298</v>
       </c>
       <c r="B19" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129000850</v>
       </c>
       <c r="B20" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>129000854</v>
       </c>
       <c r="B21" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129000851</v>
       </c>
       <c r="B22" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>129001298</v>
       </c>
       <c r="B19" t="n">
-        <v>92829</v>
+        <v>92815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2526,7 +2526,7 @@
         <v>129001298</v>
       </c>
       <c r="B19" t="n">
-        <v>92815</v>
+        <v>92816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -2420,7 +2420,7 @@
         <v>129000852</v>
       </c>
       <c r="B18" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>129001298</v>
       </c>
       <c r="B19" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129000850</v>
       </c>
       <c r="B20" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>129000854</v>
       </c>
       <c r="B21" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>129000851</v>
       </c>
       <c r="B22" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45113-2025 artfynd.xlsx
+++ b/artfynd/A 45113-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439739</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000854</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439740</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439741</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439742</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439748</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439736</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439737</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439738</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439743</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439744</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439746</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1986,6 +2051,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824954</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2087,6 +2157,11 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439745</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2184,6 +2259,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824923</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2281,6 +2361,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824939</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2378,6 +2463,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824943</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2475,6 +2565,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824947</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2572,6 +2667,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824932</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2678,6 +2778,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001298</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2779,6 +2884,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669902</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2885,6 +2995,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533092</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3004,6 +3119,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669863</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3101,6 +3221,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824935</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3198,6 +3323,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824946</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3307,6 +3437,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95669891</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3404,6 +3539,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824933</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3501,6 +3641,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111824940</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3607,6 +3752,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000852</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3713,6 +3863,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000851</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3819,6 +3974,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000850</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3920,8 +4080,47 @@
           <t>Vedsvampsinventering Sveaskog</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62439747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>